--- a/Tagihan/2026/Juli/Baim PT. Mizan.xlsx
+++ b/Tagihan/2026/Juli/Baim PT. Mizan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35C2394A-7E87-4E62-B93A-51122EECAB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDAE3BC-546C-42DE-B40C-0B752BA062AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Satu Desa" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>NO.</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>Sub Total</t>
+  </si>
+  <si>
+    <t>Ezviz H6C 3MP</t>
   </si>
 </sst>
 </file>
@@ -645,10 +648,71 @@
     <xf numFmtId="42" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -668,67 +732,6 @@
     </xf>
     <xf numFmtId="42" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -911,13 +914,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>59532</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2403475</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>172721</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1268,47 +1271,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="13"/>
@@ -1318,20 +1321,20 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="47"/>
+      <c r="G13" s="52"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="53"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="7"/>
@@ -1358,12 +1361,12 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53">
+      <c r="B17" s="55">
         <v>46127</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
     </row>
@@ -1460,12 +1463,12 @@
       <c r="G22" s="25"/>
     </row>
     <row r="23" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="56">
+      <c r="B23" s="38">
         <v>46175</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="58"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
     </row>
@@ -1541,12 +1544,12 @@
       <c r="G27" s="25"/>
     </row>
     <row r="28" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="56">
+      <c r="B28" s="38">
         <v>46186</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="58"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="40"/>
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
     </row>
@@ -1601,12 +1604,12 @@
       <c r="G31" s="25"/>
     </row>
     <row r="32" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="56">
+      <c r="B32" s="38">
         <v>46189</v>
       </c>
-      <c r="C32" s="57"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="58"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
     </row>
@@ -1640,12 +1643,12 @@
       <c r="G34" s="25"/>
     </row>
     <row r="35" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="56">
+      <c r="B35" s="38">
         <v>46195</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="58"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="25"/>
       <c r="G35" s="25"/>
     </row>
@@ -1679,12 +1682,12 @@
       <c r="G37" s="24"/>
     </row>
     <row r="38" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56">
+      <c r="B38" s="38">
         <v>46212</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="58"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="40"/>
       <c r="F38" s="25"/>
       <c r="G38" s="25"/>
     </row>
@@ -1747,13 +1750,13 @@
       <c r="G42" s="24"/>
     </row>
     <row r="43" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="61"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="49"/>
       <c r="G43" s="27">
         <f>SUM(G17:G42)</f>
         <v>36556000</v>
@@ -1768,54 +1771,49 @@
       <c r="G44" s="17"/>
     </row>
     <row r="46" spans="2:7" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B46" s="62" t="s">
+      <c r="B46" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="62"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="31"/>
       <c r="E46" s="18"/>
-      <c r="F46" s="63" t="s">
+      <c r="F46" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="63"/>
+      <c r="G46" s="51"/>
     </row>
     <row r="50" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="48"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="49" t="s">
+      <c r="B51" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="50"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="46"/>
       <c r="F51" s="20"/>
       <c r="G51" s="22"/>
       <c r="H51" s="21"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="51" t="s">
+      <c r="B52" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
       <c r="H52" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C7:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B50:G50"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="B51:E51"/>
@@ -1830,6 +1828,11 @@
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="C7:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B50:G50"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.23622047244094491" top="7.874015748031496E-2" bottom="0.74803149606299213" header="0.59055118110236227" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="85" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
@@ -1839,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{420CF71E-F188-46EA-8576-AF19D8CC87D0}">
-  <dimension ref="B5:H37"/>
+  <dimension ref="B5:H40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1855,47 +1858,47 @@
     <row r="5" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="12" spans="2:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="13"/>
@@ -1905,20 +1908,20 @@
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="47"/>
+      <c r="G13" s="52"/>
     </row>
     <row r="14" spans="2:7" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="53"/>
     </row>
     <row r="15" spans="2:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="7"/>
@@ -1945,12 +1948,12 @@
       </c>
     </row>
     <row r="17" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53">
+      <c r="B17" s="55">
         <v>46152</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
     </row>
@@ -2026,12 +2029,12 @@
       <c r="G21" s="24"/>
     </row>
     <row r="22" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="56">
+      <c r="B22" s="38">
         <v>46183</v>
       </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="58"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
     </row>
@@ -2086,112 +2089,152 @@
       <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="38">
+        <v>46230</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="25">
+        <v>450000</v>
+      </c>
+      <c r="G27" s="25">
+        <f t="shared" ref="G27" si="2">F27*D27</f>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="34">
-        <f>SUM(G18:G25)</f>
-        <v>3685000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="37" t="s">
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="34">
+        <f>SUM(G18:G28)</f>
+        <v>4585000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" s="5" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="24">
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="24">
         <v>500000</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="59" t="s">
+    <row r="31" spans="2:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="27">
-        <f>G26-G27</f>
-        <v>3185000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
-    </row>
-    <row r="31" spans="2:7" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B31" s="62" t="s">
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="27">
+        <f>G29-G30</f>
+        <v>4085000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="34" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B34" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="62"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="63" t="s">
+      <c r="C34" s="50"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="63"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="49" t="s">
+      <c r="G34" s="51"/>
+    </row>
+    <row r="38" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="21"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="51" t="s">
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="21"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F31:G31"/>
+  <mergeCells count="18">
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="F34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
